--- a/data/Almacen MB52/Combinados/Base MB52 379 - Combinado.xlsx
+++ b/data/Almacen MB52/Combinados/Base MB52 379 - Combinado.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stock_Planificacion" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stock_Planificacion'!$A$1:$AA$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stock_Planificacion'!$A$1:$AA$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA27"/>
+  <dimension ref="A1:AA40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -566,7 +566,7 @@
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
     <col width="35" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="17" customWidth="1" min="18" max="18"/>
@@ -720,11 +720,11 @@
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="4" t="n">
-        <v>1001773</v>
+        <v>1001672</v>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>CHALECOMICROPERFAMARILLOCONREFLECTIVO</t>
+          <t>ALAMBRE 4.06MM NEGRO RECOCIDO XKG</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -758,13 +758,13 @@
         </is>
       </c>
       <c r="I2" s="7" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="M2" s="8" t="n">
-        <v>37607.67</v>
+        <v>105393.07</v>
       </c>
       <c r="N2" s="5" t="inlineStr">
         <is>
@@ -781,17 +781,17 @@
       </c>
       <c r="O2" s="4" t="inlineStr">
         <is>
-          <t>SEGURIDAD</t>
+          <t>ACEROS</t>
         </is>
       </c>
       <c r="P2" s="4" t="inlineStr">
         <is>
-          <t>INDUMENTARIA</t>
+          <t>ALAMBRES</t>
         </is>
       </c>
       <c r="Q2" s="4" t="inlineStr">
         <is>
-          <t>C28</t>
+          <t>C08</t>
         </is>
       </c>
       <c r="R2" s="7" t="n">
@@ -827,11 +827,11 @@
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="9" t="n">
-        <v>1002236</v>
+        <v>1001682</v>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>BULON PARA CUCHILLA XUN</t>
+          <t>MAMEL. 1°CAL. DESC. LAMIN.BLANCO 60GR.XL</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="I3" s="11" t="n">
-        <v>44</v>
+        <v>300</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>86</v>
+        <v>600</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="M3" s="12" t="n">
-        <v>39981.64</v>
+        <v>182176.2</v>
       </c>
       <c r="N3" s="10" t="inlineStr">
         <is>
@@ -888,17 +888,17 @@
       </c>
       <c r="O3" s="9" t="inlineStr">
         <is>
-          <t>DESGASTE</t>
+          <t>SEGURIDAD</t>
         </is>
       </c>
       <c r="P3" s="9" t="inlineStr">
         <is>
-          <t>CAT 140K // CAT 988H // CAT D6T</t>
+          <t>INDUMENTARIA</t>
         </is>
       </c>
       <c r="Q3" s="9" t="inlineStr">
         <is>
-          <t>G05</t>
+          <t>C28</t>
         </is>
       </c>
       <c r="R3" s="11" t="n">
@@ -934,11 +934,11 @@
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="4" t="n">
-        <v>1002236</v>
+        <v>1001701</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>BULON PARA CUCHILLA XUN</t>
+          <t>GUANTE NITRILO AZUL PUÑO ELASTIZADO</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -972,13 +972,13 @@
         </is>
       </c>
       <c r="I4" s="7" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="M4" s="8" t="n">
-        <v>18938.67</v>
+        <v>13912.71</v>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
@@ -995,17 +995,17 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>DESGASTE</t>
+          <t>SEGURIDAD</t>
         </is>
       </c>
       <c r="P4" s="4" t="inlineStr">
         <is>
-          <t>CAT 140K // CAT 988H // CAT D6T</t>
+          <t>GUANTE</t>
         </is>
       </c>
       <c r="Q4" s="4" t="inlineStr">
         <is>
-          <t>G05</t>
+          <t>C28</t>
         </is>
       </c>
       <c r="R4" s="7" t="n">
@@ -1041,11 +1041,11 @@
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="9" t="n">
-        <v>1002340</v>
+        <v>1001707</v>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>BULON 5/8 X 21/2</t>
+          <t>CHALECOGRAFANARANJACONREFLETIVOT.XLC2</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -1079,13 +1079,13 @@
         </is>
       </c>
       <c r="I5" s="11" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="M5" s="12" t="n">
-        <v>68294.47</v>
+        <v>361165.6</v>
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="O5" s="9" t="inlineStr">
         <is>
-          <t>DESGASTE</t>
+          <t>SEGURIDAD</t>
         </is>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>JD 770D/CAT 140K</t>
+          <t>INDUMENTARIA</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>G05</t>
+          <t>C28</t>
         </is>
       </c>
       <c r="R5" s="11" t="n">
@@ -1148,11 +1148,11 @@
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>1002353</v>
+        <v>1001708</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>TUERCA 5 8</t>
+          <t>GUANTE POLIAMIDA LAMINADO PALMAPU-TALLE9</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -1186,13 +1186,13 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>90</v>
+        <v>350</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>172</v>
+        <v>600</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="M6" s="8" t="n">
-        <v>147408.47</v>
+        <v>9470.209999999999</v>
       </c>
       <c r="N6" s="5" t="inlineStr">
         <is>
@@ -1209,17 +1209,17 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>DESGASTE</t>
+          <t>SEGURIDAD</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>JD 770 670 CAT 140H</t>
+          <t>GUANTE</t>
         </is>
       </c>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t>G05</t>
+          <t>C28</t>
         </is>
       </c>
       <c r="R6" s="7" t="n">
@@ -1255,11 +1255,11 @@
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="9" t="n">
-        <v>1004590</v>
+        <v>1001708</v>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>SEGURO P T70286 3 4 P CUCHILLA</t>
+          <t>GUANTE POLIAMIDA LAMINADO PALMAPU-TALLE9</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="I7" s="11" t="n">
-        <v>24</v>
+        <v>350</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>48</v>
+        <v>600</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="L7" s="10" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="M7" s="12" t="n">
-        <v>54240.28</v>
+        <v>29867.57</v>
       </c>
       <c r="N7" s="10" t="inlineStr">
         <is>
@@ -1316,17 +1316,17 @@
       </c>
       <c r="O7" s="9" t="inlineStr">
         <is>
-          <t>DESGASTE</t>
+          <t>SEGURIDAD</t>
         </is>
       </c>
       <c r="P7" s="9" t="inlineStr">
         <is>
-          <t>JD850J</t>
+          <t>GUANTE</t>
         </is>
       </c>
       <c r="Q7" s="9" t="inlineStr">
         <is>
-          <t>G05</t>
+          <t>C28</t>
         </is>
       </c>
       <c r="R7" s="11" t="n">
@@ -1362,11 +1362,11 @@
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>1009475</v>
+        <v>1001716</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>PANTALON TERMICO "ROJO" T M</t>
+          <t>TAPON AUDITIVO</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1384,29 +1384,29 @@
           <t>379</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>NO PLANIFICADO</t>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>V1</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>NO PLANIFICADO</t>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
         </is>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="M8" s="8" t="n">
-        <v>57794.08</v>
+        <v>22018.15</v>
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>ROPA</t>
+          <t>SEGURIDAD</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>INDUMENTARIA -15</t>
+          <t>ACCESORIO SEGURIDAD</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
@@ -1469,11 +1469,11 @@
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="9" t="n">
-        <v>1009476</v>
+        <v>1001773</v>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>PANTALON TERMICO "ROJO" T L</t>
+          <t>CHALECOMICROPERFAMARILLOCONREFLECTIVO</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -1491,29 +1491,29 @@
           <t>379</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>NO PLANIFICADO</t>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>V1</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>NO PLANIFICADO</t>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
         </is>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="L9" s="10" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="M9" s="12" t="n">
-        <v>206590.8</v>
+        <v>37607.67</v>
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="O9" s="9" t="inlineStr">
         <is>
-          <t>ROPA</t>
+          <t>SEGURIDAD</t>
         </is>
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>INDUMENTARIA -15</t>
+          <t>INDUMENTARIA</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
@@ -1576,11 +1576,11 @@
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>1009478</v>
+        <v>1001895</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>PANTALON TERMICO "ROJO" T XXL</t>
+          <t>ALCOHOL LIQUIDO X LITRO</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1598,29 +1598,29 @@
           <t>379</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>NO PLANIFICADO</t>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>V1</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>NO PLANIFICADO</t>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
         </is>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="M10" s="8" t="n">
-        <v>96814.36</v>
+        <v>16762.06</v>
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>ROPA</t>
+          <t>LIMPIEZA</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>INDUMENTARIA -15</t>
+          <t>ALCOHOL LIQUIDO</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>C28</t>
+          <t>C17</t>
         </is>
       </c>
       <c r="R10" s="7" t="n">
@@ -1683,11 +1683,11 @@
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="9" t="n">
-        <v>1009479</v>
+        <v>1002236</v>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>PANTALON TERMICO "ROJO" T XXXL</t>
+          <t>BULON PARA CUCHILLA XUN</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -1705,29 +1705,29 @@
           <t>379</t>
         </is>
       </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G11" s="13" t="inlineStr">
-        <is>
-          <t>NO PLANIFICADO</t>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>V1</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>NO PLANIFICADO</t>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
         </is>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="M11" s="12" t="n">
-        <v>90737.21000000001</v>
+        <v>39981.64</v>
       </c>
       <c r="N11" s="10" t="inlineStr">
         <is>
@@ -1744,17 +1744,17 @@
       </c>
       <c r="O11" s="9" t="inlineStr">
         <is>
-          <t>ROPA</t>
+          <t>DESGASTE</t>
         </is>
       </c>
       <c r="P11" s="9" t="inlineStr">
         <is>
-          <t>INDUMENTARIA -15</t>
+          <t>CAT 140K // CAT 988H // CAT D6T</t>
         </is>
       </c>
       <c r="Q11" s="9" t="inlineStr">
         <is>
-          <t>C28</t>
+          <t>G05</t>
         </is>
       </c>
       <c r="R11" s="11" t="n">
@@ -1790,11 +1790,11 @@
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>1009479</v>
+        <v>1002236</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>PANTALON TERMICO "ROJO" T XXXL</t>
+          <t>BULON PARA CUCHILLA XUN</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -1812,29 +1812,29 @@
           <t>379</t>
         </is>
       </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G12" s="13" t="inlineStr">
-        <is>
-          <t>NO PLANIFICADO</t>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>V1</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>NO PLANIFICADO</t>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
         </is>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="M12" s="8" t="n">
-        <v>30245.74</v>
+        <v>18938.67</v>
       </c>
       <c r="N12" s="5" t="inlineStr">
         <is>
@@ -1851,17 +1851,17 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>ROPA</t>
+          <t>DESGASTE</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>INDUMENTARIA -15</t>
+          <t>CAT 140K // CAT 988H // CAT D6T</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>C28</t>
+          <t>G05</t>
         </is>
       </c>
       <c r="R12" s="7" t="n">
@@ -1897,11 +1897,11 @@
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="9" t="n">
-        <v>1009530</v>
+        <v>1002340</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>BATERIAS DE REPUESTO P/BALIZA 1000 HORAS</t>
+          <t>BULON 5/8 X 21/2</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>04-MAYOR A STOCK MAXIMO</t>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
         </is>
       </c>
       <c r="I13" s="11" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>25</v>
+        <v>172</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="L13" s="10" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="M13" s="12" t="n">
-        <v>12294.06</v>
+        <v>68294.47</v>
       </c>
       <c r="N13" s="10" t="inlineStr">
         <is>
@@ -1958,17 +1958,17 @@
       </c>
       <c r="O13" s="9" t="inlineStr">
         <is>
-          <t>SEGURIDAD</t>
+          <t>DESGASTE</t>
         </is>
       </c>
       <c r="P13" s="9" t="inlineStr">
         <is>
-          <t>INSUMOS</t>
+          <t>JD 770D/CAT 140K</t>
         </is>
       </c>
       <c r="Q13" s="9" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>G05</t>
         </is>
       </c>
       <c r="R13" s="11" t="n">
@@ -2004,11 +2004,11 @@
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>1009530</v>
+        <v>1002353</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>BATERIAS DE REPUESTO P/BALIZA 1000 HORAS</t>
+          <t>TUERCA 5 8</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -2038,17 +2038,17 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>04-MAYOR A STOCK MAXIMO</t>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
         </is>
       </c>
       <c r="I14" s="7" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>25</v>
+        <v>172</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="M14" s="8" t="n">
-        <v>159822.76</v>
+        <v>147408.47</v>
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
@@ -2065,17 +2065,17 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>SEGURIDAD</t>
+          <t>DESGASTE</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>INSUMOS</t>
+          <t>JD 770 670 CAT 140H</t>
         </is>
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>G05</t>
         </is>
       </c>
       <c r="R14" s="7" t="n">
@@ -2111,16 +2111,16 @@
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="9" t="n">
-        <v>1012896</v>
+        <v>1004590</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>INSUMO FERRETERIA S DETALLE</t>
+          <t>SEGURO P T70286 3 4 P CUCHILLA</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>ZGEN</t>
+          <t>ZSTO</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
@@ -2133,29 +2133,29 @@
           <t>379</t>
         </is>
       </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G15" s="13" t="inlineStr">
-        <is>
-          <t>NO PLANIFICADO</t>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>V1</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>NO PLANIFICADO</t>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
         </is>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0</v>
+        <v>54240.28</v>
       </c>
       <c r="N15" s="10" t="inlineStr">
         <is>
@@ -2172,13 +2172,17 @@
       </c>
       <c r="O15" s="9" t="inlineStr">
         <is>
-          <t>SIN RUBRO</t>
-        </is>
-      </c>
-      <c r="P15" s="9" t="inlineStr"/>
+          <t>DESGASTE</t>
+        </is>
+      </c>
+      <c r="P15" s="9" t="inlineStr">
+        <is>
+          <t>JD850J</t>
+        </is>
+      </c>
       <c r="Q15" s="9" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>G05</t>
         </is>
       </c>
       <c r="R15" s="11" t="n">
@@ -2214,11 +2218,11 @@
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>1016724</v>
+        <v>1009471</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>BOTA SEGURIDAD P/ NIEVE IMPERMEABLE T42</t>
+          <t>ANTEOJO TRANSPARENTE H/C</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -2236,29 +2240,29 @@
           <t>379</t>
         </is>
       </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G16" s="13" t="inlineStr">
-        <is>
-          <t>NO PLANIFICADO</t>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>V1</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>NO PLANIFICADO</t>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
         </is>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
@@ -2266,7 +2270,7 @@
         </is>
       </c>
       <c r="M16" s="8" t="n">
-        <v>51616.13</v>
+        <v>40045.6</v>
       </c>
       <c r="N16" s="5" t="inlineStr">
         <is>
@@ -2275,10 +2279,14 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>SIN RUBRO</t>
-        </is>
-      </c>
-      <c r="P16" s="4" t="inlineStr"/>
+          <t>SEGURIDAD</t>
+        </is>
+      </c>
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t>ACCESORIO SEGURIDAD</t>
+        </is>
+      </c>
       <c r="Q16" s="4" t="inlineStr">
         <is>
           <t>C28</t>
@@ -2317,11 +2325,11 @@
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="9" t="n">
-        <v>1016725</v>
+        <v>1009471</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>BOTA SEGURIDAD P/ NIEVE IMPERMEABLE T43</t>
+          <t>ANTEOJO TRANSPARENTE H/C</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -2339,29 +2347,29 @@
           <t>379</t>
         </is>
       </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G17" s="13" t="inlineStr">
-        <is>
-          <t>NO PLANIFICADO</t>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>V1</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>NO PLANIFICADO</t>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
         </is>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
@@ -2369,7 +2377,7 @@
         </is>
       </c>
       <c r="M17" s="12" t="n">
-        <v>260096.84</v>
+        <v>24544.08</v>
       </c>
       <c r="N17" s="10" t="inlineStr">
         <is>
@@ -2378,10 +2386,14 @@
       </c>
       <c r="O17" s="9" t="inlineStr">
         <is>
-          <t>SIN RUBRO</t>
-        </is>
-      </c>
-      <c r="P17" s="9" t="inlineStr"/>
+          <t>SEGURIDAD</t>
+        </is>
+      </c>
+      <c r="P17" s="9" t="inlineStr">
+        <is>
+          <t>ACCESORIO SEGURIDAD</t>
+        </is>
+      </c>
       <c r="Q17" s="9" t="inlineStr">
         <is>
           <t>C28</t>
@@ -2420,11 +2432,11 @@
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>1016726</v>
+        <v>1009475</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>BOTA SEGURIDAD P/ NIEVE IMPERMEABLE T44</t>
+          <t>PANTALON TERMICO "ROJO" T M</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -2464,7 +2476,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
@@ -2472,7 +2484,7 @@
         </is>
       </c>
       <c r="M18" s="8" t="n">
-        <v>130616.62</v>
+        <v>57794.08</v>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
@@ -2481,10 +2493,14 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>SIN RUBRO</t>
-        </is>
-      </c>
-      <c r="P18" s="4" t="inlineStr"/>
+          <t>ROPA</t>
+        </is>
+      </c>
+      <c r="P18" s="4" t="inlineStr">
+        <is>
+          <t>INDUMENTARIA -15</t>
+        </is>
+      </c>
       <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>C28</t>
@@ -2523,11 +2539,11 @@
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="9" t="n">
-        <v>1016727</v>
+        <v>1009476</v>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>BOTA SEGURIDAD P/ NIEVE IMPERMEABLE T45</t>
+          <t>PANTALON TERMICO "ROJO" T L</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -2567,7 +2583,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
@@ -2575,7 +2591,7 @@
         </is>
       </c>
       <c r="M19" s="12" t="n">
-        <v>34587.32</v>
+        <v>206590.8</v>
       </c>
       <c r="N19" s="10" t="inlineStr">
         <is>
@@ -2584,10 +2600,14 @@
       </c>
       <c r="O19" s="9" t="inlineStr">
         <is>
-          <t>SIN RUBRO</t>
-        </is>
-      </c>
-      <c r="P19" s="9" t="inlineStr"/>
+          <t>ROPA</t>
+        </is>
+      </c>
+      <c r="P19" s="9" t="inlineStr">
+        <is>
+          <t>INDUMENTARIA -15</t>
+        </is>
+      </c>
       <c r="Q19" s="9" t="inlineStr">
         <is>
           <t>C28</t>
@@ -2626,11 +2646,11 @@
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>1022874</v>
+        <v>1009478</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CUCHILLA CENTRAL</t>
+          <t>PANTALON TERMICO "ROJO" T XXL</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -2648,26 +2668,26 @@
           <t>379</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>V1</t>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>NO PLANIFICADO</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>02-MENOR A PUNTO DE PEDIDO</t>
+          <t>NO PLANIFICADO</t>
         </is>
       </c>
       <c r="I20" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K20" s="7" t="n">
         <v>2</v>
@@ -2678,7 +2698,7 @@
         </is>
       </c>
       <c r="M20" s="8" t="n">
-        <v>764268.39</v>
+        <v>96814.36</v>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
@@ -2687,17 +2707,17 @@
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>DESGASTE</t>
+          <t>ROPA</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>JD850J</t>
+          <t>INDUMENTARIA -15</t>
         </is>
       </c>
       <c r="Q20" s="4" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>C28</t>
         </is>
       </c>
       <c r="R20" s="7" t="n">
@@ -2733,11 +2753,11 @@
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="9" t="n">
-        <v>1025549</v>
+        <v>1009479</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>BORDE CORTANTE (LH)</t>
+          <t>PANTALON TERMICO "ROJO" T XXXL</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -2755,29 +2775,29 @@
           <t>379</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>V1</t>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>NO PLANIFICADO</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>02-MENOR A PUNTO DE PEDIDO</t>
+          <t>NO PLANIFICADO</t>
         </is>
       </c>
       <c r="I21" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
@@ -2785,7 +2805,7 @@
         </is>
       </c>
       <c r="M21" s="12" t="n">
-        <v>175125.81</v>
+        <v>90737.21000000001</v>
       </c>
       <c r="N21" s="10" t="inlineStr">
         <is>
@@ -2794,17 +2814,17 @@
       </c>
       <c r="O21" s="9" t="inlineStr">
         <is>
-          <t>DESGASTE</t>
+          <t>ROPA</t>
         </is>
       </c>
       <c r="P21" s="9" t="inlineStr">
         <is>
-          <t>JD850J</t>
+          <t>INDUMENTARIA -15</t>
         </is>
       </c>
       <c r="Q21" s="9" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>C28</t>
         </is>
       </c>
       <c r="R21" s="11" t="n">
@@ -2840,11 +2860,11 @@
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>1025550</v>
+        <v>1009479</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>BORDE CORTANTE (RH)</t>
+          <t>PANTALON TERMICO "ROJO" T XXXL</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -2862,26 +2882,26 @@
           <t>379</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>V1</t>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>NO PLANIFICADO</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>02-MENOR A PUNTO DE PEDIDO</t>
+          <t>NO PLANIFICADO</t>
         </is>
       </c>
       <c r="I22" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K22" s="7" t="n">
         <v>1</v>
@@ -2892,7 +2912,7 @@
         </is>
       </c>
       <c r="M22" s="8" t="n">
-        <v>181460.47</v>
+        <v>30245.74</v>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
@@ -2901,17 +2921,17 @@
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>DESGASTE</t>
+          <t>ROPA</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>JD850J</t>
+          <t>INDUMENTARIA -15</t>
         </is>
       </c>
       <c r="Q22" s="4" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>C28</t>
         </is>
       </c>
       <c r="R22" s="7" t="n">
@@ -2947,11 +2967,11 @@
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="9" t="n">
-        <v>1025731</v>
+        <v>1009481</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>BULON PARA DESGASTES DE ESPEJO</t>
+          <t>ANTEOJO GRIS H/C</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
@@ -2985,13 +3005,13 @@
         </is>
       </c>
       <c r="I23" s="11" t="n">
-        <v>24</v>
+        <v>250</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
@@ -2999,7 +3019,7 @@
         </is>
       </c>
       <c r="M23" s="12" t="n">
-        <v>220641.71</v>
+        <v>64931.43</v>
       </c>
       <c r="N23" s="10" t="inlineStr">
         <is>
@@ -3008,17 +3028,17 @@
       </c>
       <c r="O23" s="9" t="inlineStr">
         <is>
-          <t>DESGASTE</t>
+          <t>SEGURIDAD</t>
         </is>
       </c>
       <c r="P23" s="9" t="inlineStr">
         <is>
-          <t>JD850J</t>
+          <t>INDUMENTARIA</t>
         </is>
       </c>
       <c r="Q23" s="9" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>C28</t>
         </is>
       </c>
       <c r="R23" s="11" t="n">
@@ -3054,11 +3074,11 @@
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>1036861</v>
+        <v>1009530</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>REP. ARRANQUE CAT D6</t>
+          <t>BATERIAS DE REPUESTO P/BALIZA 1000 HORAS</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -3076,29 +3096,29 @@
           <t>379</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>NO PLANIFICADO</t>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>V1</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>NO PLANIFICADO</t>
+          <t>04-MAYOR A STOCK MAXIMO</t>
         </is>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
@@ -3106,7 +3126,7 @@
         </is>
       </c>
       <c r="M24" s="8" t="n">
-        <v>4573711.41</v>
+        <v>12294.06</v>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
@@ -3115,13 +3135,17 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>SIN RUBRO</t>
-        </is>
-      </c>
-      <c r="P24" s="4" t="inlineStr"/>
+          <t>SEGURIDAD</t>
+        </is>
+      </c>
+      <c r="P24" s="4" t="inlineStr">
+        <is>
+          <t>INSUMOS</t>
+        </is>
+      </c>
       <c r="Q24" s="4" t="inlineStr">
         <is>
-          <t>C04</t>
+          <t>C03</t>
         </is>
       </c>
       <c r="R24" s="7" t="n">
@@ -3157,11 +3181,11 @@
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="9" t="n">
-        <v>1040975</v>
+        <v>1009530</v>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>REP.MOTOR DE ARRANQUE (770G)</t>
+          <t>BATERIAS DE REPUESTO P/BALIZA 1000 HORAS</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -3179,29 +3203,29 @@
           <t>379</t>
         </is>
       </c>
-      <c r="F25" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G25" s="13" t="inlineStr">
-        <is>
-          <t>NO PLANIFICADO</t>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>V1</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>NO PLANIFICADO</t>
+          <t>04-MAYOR A STOCK MAXIMO</t>
         </is>
       </c>
       <c r="I25" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
@@ -3209,7 +3233,7 @@
         </is>
       </c>
       <c r="M25" s="12" t="n">
-        <v>158893.14</v>
+        <v>159822.76</v>
       </c>
       <c r="N25" s="10" t="inlineStr">
         <is>
@@ -3218,13 +3242,17 @@
       </c>
       <c r="O25" s="9" t="inlineStr">
         <is>
-          <t>SIN RUBRO</t>
-        </is>
-      </c>
-      <c r="P25" s="9" t="inlineStr"/>
+          <t>SEGURIDAD</t>
+        </is>
+      </c>
+      <c r="P25" s="9" t="inlineStr">
+        <is>
+          <t>INSUMOS</t>
+        </is>
+      </c>
       <c r="Q25" s="9" t="inlineStr">
         <is>
-          <t>C04</t>
+          <t>C03</t>
         </is>
       </c>
       <c r="R25" s="11" t="n">
@@ -3260,16 +3288,16 @@
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>1041585</v>
+        <v>1012896</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>REP. MOTOR DE ARRANQUE CAT 950</t>
+          <t>INSUMO FERRETERIA S DETALLE</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>ZSTO</t>
+          <t>ZGEN</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -3304,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
@@ -3312,7 +3340,7 @@
         </is>
       </c>
       <c r="M26" s="8" t="n">
-        <v>1065145.93</v>
+        <v>0</v>
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
@@ -3327,7 +3355,7 @@
       <c r="P26" s="4" t="inlineStr"/>
       <c r="Q26" s="4" t="inlineStr">
         <is>
-          <t>C04</t>
+          <t>C13</t>
         </is>
       </c>
       <c r="R26" s="7" t="n">
@@ -3363,113 +3391,1480 @@
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="9" t="n">
+        <v>1015947</v>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>REPUESTO GENERICO</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>ZGEN</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>MM01</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>NO PLANIFICADO</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>NO PLANIFICADO</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="L27" s="10" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="M27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="O27" s="9" t="inlineStr">
+        <is>
+          <t>SIN RUBRO</t>
+        </is>
+      </c>
+      <c r="P27" s="9" t="inlineStr"/>
+      <c r="Q27" s="9" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="R27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="4" t="n">
+        <v>1016724</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>BOTA SEGURIDAD P/ NIEVE IMPERMEABLE T42</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>ZSTO</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>MM01</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>NO PLANIFICADO</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>NO PLANIFICADO</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="n">
+        <v>51616.13</v>
+      </c>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>SIN RUBRO</t>
+        </is>
+      </c>
+      <c r="P28" s="4" t="inlineStr"/>
+      <c r="Q28" s="4" t="inlineStr">
+        <is>
+          <t>C28</t>
+        </is>
+      </c>
+      <c r="R28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="9" t="n">
+        <v>1016725</v>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>BOTA SEGURIDAD P/ NIEVE IMPERMEABLE T43</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>ZSTO</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>MM01</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>NO PLANIFICADO</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>NO PLANIFICADO</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L29" s="10" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="M29" s="12" t="n">
+        <v>208077.47</v>
+      </c>
+      <c r="N29" s="10" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="O29" s="9" t="inlineStr">
+        <is>
+          <t>SIN RUBRO</t>
+        </is>
+      </c>
+      <c r="P29" s="9" t="inlineStr"/>
+      <c r="Q29" s="9" t="inlineStr">
+        <is>
+          <t>C28</t>
+        </is>
+      </c>
+      <c r="R29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="4" t="n">
+        <v>1016726</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>BOTA SEGURIDAD P/ NIEVE IMPERMEABLE T44</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>ZSTO</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>MM01</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>NO PLANIFICADO</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>NO PLANIFICADO</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="M30" s="8" t="n">
+        <v>111957.1</v>
+      </c>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>SIN RUBRO</t>
+        </is>
+      </c>
+      <c r="P30" s="4" t="inlineStr"/>
+      <c r="Q30" s="4" t="inlineStr">
+        <is>
+          <t>C28</t>
+        </is>
+      </c>
+      <c r="R30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="9" t="n">
+        <v>1016727</v>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>BOTA SEGURIDAD P/ NIEVE IMPERMEABLE T45</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>ZSTO</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>MM01</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>NO PLANIFICADO</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>NO PLANIFICADO</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" s="10" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="M31" s="12" t="n">
+        <v>17293.66</v>
+      </c>
+      <c r="N31" s="10" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="O31" s="9" t="inlineStr">
+        <is>
+          <t>SIN RUBRO</t>
+        </is>
+      </c>
+      <c r="P31" s="9" t="inlineStr"/>
+      <c r="Q31" s="9" t="inlineStr">
+        <is>
+          <t>C28</t>
+        </is>
+      </c>
+      <c r="R31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="4" t="n">
+        <v>1016894</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>MAMEL. 1°CAL. DESC. LAMIN.BLANCO 60GRXXL</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>ZSTO</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>MM01</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="M32" s="8" t="n">
+        <v>229469.75</v>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>SEGURIDAD</t>
+        </is>
+      </c>
+      <c r="P32" s="4" t="inlineStr">
+        <is>
+          <t>INDUMENTARIA</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr">
+        <is>
+          <t>C28</t>
+        </is>
+      </c>
+      <c r="R32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="9" t="n">
+        <v>1017031</v>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>GUANTES ALTO IMPACTO X PAR</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>ZSSD</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>MM01</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="n">
+        <v>150</v>
+      </c>
+      <c r="J33" s="11" t="n">
+        <v>350</v>
+      </c>
+      <c r="K33" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="L33" s="10" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="M33" s="12" t="n">
+        <v>139140.21</v>
+      </c>
+      <c r="N33" s="10" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="O33" s="9" t="inlineStr">
+        <is>
+          <t>INDUMENTARIA</t>
+        </is>
+      </c>
+      <c r="P33" s="9" t="inlineStr">
+        <is>
+          <t>EPP</t>
+        </is>
+      </c>
+      <c r="Q33" s="9" t="inlineStr">
+        <is>
+          <t>C28</t>
+        </is>
+      </c>
+      <c r="R33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="4" t="n">
+        <v>1022874</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>CUCHILLA CENTRAL</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>ZSTO</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>MM01</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K34" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="M34" s="8" t="n">
+        <v>764268.39</v>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>DESGASTE</t>
+        </is>
+      </c>
+      <c r="P34" s="4" t="inlineStr">
+        <is>
+          <t>JD850J</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="R34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="9" t="n">
+        <v>1025549</v>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>BORDE CORTANTE (LH)</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>ZSTO</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>MM01</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K35" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" s="10" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="M35" s="12" t="n">
+        <v>175125.81</v>
+      </c>
+      <c r="N35" s="10" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="O35" s="9" t="inlineStr">
+        <is>
+          <t>DESGASTE</t>
+        </is>
+      </c>
+      <c r="P35" s="9" t="inlineStr">
+        <is>
+          <t>JD850J</t>
+        </is>
+      </c>
+      <c r="Q35" s="9" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="R35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="4" t="n">
+        <v>1025550</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>BORDE CORTANTE (RH)</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>ZSTO</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>MM01</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>181460.47</v>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>DESGASTE</t>
+        </is>
+      </c>
+      <c r="P36" s="4" t="inlineStr">
+        <is>
+          <t>JD850J</t>
+        </is>
+      </c>
+      <c r="Q36" s="4" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="R36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="9" t="n">
+        <v>1025731</v>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>BULON PARA DESGASTES DE ESPEJO</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>ZSTO</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>MM01</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="J37" s="11" t="n">
+        <v>48</v>
+      </c>
+      <c r="K37" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="L37" s="10" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="M37" s="12" t="n">
+        <v>220641.71</v>
+      </c>
+      <c r="N37" s="10" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="O37" s="9" t="inlineStr">
+        <is>
+          <t>DESGASTE</t>
+        </is>
+      </c>
+      <c r="P37" s="9" t="inlineStr">
+        <is>
+          <t>JD850J</t>
+        </is>
+      </c>
+      <c r="Q37" s="9" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="R37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="4" t="n">
+        <v>1040975</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>REP.MOTOR DE ARRANQUE (770G)</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>ZSTO</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>MM01</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>NO PLANIFICADO</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>NO PLANIFICADO</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="M38" s="8" t="n">
+        <v>158893.14</v>
+      </c>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>SIN RUBRO</t>
+        </is>
+      </c>
+      <c r="P38" s="4" t="inlineStr"/>
+      <c r="Q38" s="4" t="inlineStr">
+        <is>
+          <t>C04</t>
+        </is>
+      </c>
+      <c r="R38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="9" t="n">
         <v>1041725</v>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>CUCHILLA (7′ X 8″ X 5/8″) X 15 Aguj 5/8"</t>
         </is>
       </c>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>ZSTO</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D39" s="10" t="inlineStr">
         <is>
           <t>MM01</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="E39" s="10" t="inlineStr">
         <is>
           <t>379</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>V1</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H39" s="9" t="inlineStr">
         <is>
           <t>02-MENOR A PUNTO DE PEDIDO</t>
         </is>
       </c>
-      <c r="I27" s="11" t="n">
+      <c r="I39" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="J27" s="11" t="n">
+      <c r="J39" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="K27" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L27" s="10" t="inlineStr">
+      <c r="K39" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
         <is>
           <t>UN</t>
         </is>
       </c>
-      <c r="M27" s="12" t="n">
-        <v>753841.77</v>
-      </c>
-      <c r="N27" s="10" t="inlineStr">
+      <c r="M39" s="12" t="n">
+        <v>376920.88</v>
+      </c>
+      <c r="N39" s="10" t="inlineStr">
         <is>
           <t>ARS</t>
         </is>
       </c>
-      <c r="O27" s="9" t="inlineStr">
+      <c r="O39" s="9" t="inlineStr">
         <is>
           <t>EQUIPOS</t>
         </is>
       </c>
-      <c r="P27" s="9" t="inlineStr">
+      <c r="P39" s="9" t="inlineStr">
         <is>
           <t>DESGASTE</t>
         </is>
       </c>
-      <c r="Q27" s="9" t="inlineStr">
+      <c r="Q39" s="9" t="inlineStr">
         <is>
           <t>C03</t>
         </is>
       </c>
-      <c r="R27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="12" t="n">
+      <c r="R39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="4" t="n">
+        <v>1056086</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>BOLIGRAFO TRAZO GRUESO AZUL</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>ZSTO</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>MM01</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>03-MAYOR A PUNTO DE PEDIDO</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J40" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="K40" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+      <c r="M40" s="8" t="n">
+        <v>10350.99</v>
+      </c>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>LIBRERIA</t>
+        </is>
+      </c>
+      <c r="P40" s="4" t="inlineStr">
+        <is>
+          <t>ESCRITURA</t>
+        </is>
+      </c>
+      <c r="Q40" s="4" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="R40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="8" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA27"/>
+  <autoFilter ref="A1:AA40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/Almacen MB52/Combinados/Base MB52 379 - Combinado.xlsx
+++ b/data/Almacen MB52/Combinados/Base MB52 379 - Combinado.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stock_Planificacion" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stock_Planificacion'!$A$1:$R$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stock_Planificacion'!$A$1:$R$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R61"/>
+  <dimension ref="A1:R56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -789,7 +789,7 @@
         <v>600</v>
       </c>
       <c r="L3" s="11" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="N3" s="12" t="n">
-        <v>569300.62</v>
+        <v>561709.95</v>
       </c>
       <c r="O3" s="10" t="inlineStr">
         <is>
@@ -822,11 +822,11 @@
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="4" t="n">
-        <v>1001682</v>
+        <v>1001701</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>MAMEL. 1°CAL. DESC. LAMIN.BLANCO 60GR.XL</t>
+          <t>GUANTE NITRILO AZUL PUÑO ELASTIZADO</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="J4" s="7" t="n">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>600</v>
+        <v>20</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="N4" s="8" t="n">
-        <v>166994.85</v>
+        <v>13912.71</v>
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
       </c>
       <c r="Q4" s="4" t="inlineStr">
         <is>
-          <t>INDUMENTARIA</t>
+          <t>GUANTE</t>
         </is>
       </c>
       <c r="R4" s="4" t="inlineStr">
@@ -900,11 +900,11 @@
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="9" t="n">
-        <v>1001701</v>
+        <v>1001707</v>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>GUANTE NITRILO AZUL PUÑO ELASTIZADO</t>
+          <t>CHALECOGRAFANARANJACONREFLETIVOT.XLC2</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="J5" s="11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="L5" s="11" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="N5" s="12" t="n">
-        <v>13912.71</v>
+        <v>325049.04</v>
       </c>
       <c r="O5" s="10" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>GUANTE</t>
+          <t>INDUMENTARIA</t>
         </is>
       </c>
       <c r="R5" s="9" t="inlineStr">
@@ -978,11 +978,11 @@
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>1001707</v>
+        <v>1001708</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CHALECOGRAFANARANJACONREFLETIVOT.XLC2</t>
+          <t>GUANTE POLIAMIDA LAMINADO PALMAPU-TALLE9</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="J6" s="7" t="n">
-        <v>50</v>
+        <v>350</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="N6" s="8" t="n">
-        <v>361165.6</v>
+        <v>13841.07</v>
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t>INDUMENTARIA</t>
+          <t>GUANTE</t>
         </is>
       </c>
       <c r="R6" s="4" t="inlineStr">
@@ -1101,7 +1101,7 @@
         <v>600</v>
       </c>
       <c r="L7" s="11" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="N7" s="12" t="n">
-        <v>17483.46</v>
+        <v>8741.73</v>
       </c>
       <c r="O7" s="10" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>600</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="N8" s="8" t="n">
-        <v>8741.73</v>
+        <v>29867.57</v>
       </c>
       <c r="O8" s="5" t="inlineStr">
         <is>
@@ -1212,11 +1212,11 @@
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="9" t="n">
-        <v>1001708</v>
+        <v>1001716</v>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>GUANTE POLIAMIDA LAMINADO PALMAPU-TALLE9</t>
+          <t>TAPON AUDITIVO</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -1251,13 +1251,13 @@
         </is>
       </c>
       <c r="J9" s="11" t="n">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="L9" s="11" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         </is>
       </c>
       <c r="N9" s="12" t="n">
-        <v>29867.57</v>
+        <v>20612.74</v>
       </c>
       <c r="O9" s="10" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>GUANTE</t>
+          <t>ACCESORIO SEGURIDAD</t>
         </is>
       </c>
       <c r="R9" s="9" t="inlineStr">
@@ -1290,11 +1290,11 @@
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>1001716</v>
+        <v>1001773</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>TAPON AUDITIVO</t>
+          <t>CHALECOMICROPERFAMARILLOCONREFLECTIVO</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1335,7 +1335,7 @@
         <v>200</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="N10" s="8" t="n">
-        <v>22018.15</v>
+        <v>3760.77</v>
       </c>
       <c r="O10" s="5" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>ACCESORIO SEGURIDAD</t>
+          <t>INDUMENTARIA</t>
         </is>
       </c>
       <c r="R10" s="4" t="inlineStr">
@@ -1446,11 +1446,11 @@
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>1001773</v>
+        <v>1001778</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CHALECOMICROPERFAMARILLOCONREFLECTIVO</t>
+          <t>YERBA MATE X 500GRS X UN</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -1485,13 +1485,13 @@
         </is>
       </c>
       <c r="J12" s="7" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="N12" s="8" t="n">
-        <v>37607.67</v>
+        <v>58547.26</v>
       </c>
       <c r="O12" s="5" t="inlineStr">
         <is>
@@ -1508,27 +1508,27 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>SEGURIDAD</t>
+          <t>ALIMENTOS</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>INDUMENTARIA</t>
+          <t>?</t>
         </is>
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
-          <t>C28</t>
+          <t>C17</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="9" t="n">
-        <v>1001778</v>
+        <v>1001895</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>YERBA MATE X 500GRS X UN</t>
+          <t>ALCOHOL LIQUIDO X LITRO</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -1559,17 +1559,17 @@
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>01-STOCK NULO</t>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
         </is>
       </c>
       <c r="J13" s="11" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="L13" s="11" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="N13" s="12" t="n">
-        <v>86098.91</v>
+        <v>30171.7</v>
       </c>
       <c r="O13" s="10" t="inlineStr">
         <is>
@@ -1586,12 +1586,12 @@
       </c>
       <c r="P13" s="9" t="inlineStr">
         <is>
-          <t>ALIMENTOS</t>
+          <t>LIMPIEZA</t>
         </is>
       </c>
       <c r="Q13" s="9" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>ALCOHOL LIQUIDO</t>
         </is>
       </c>
       <c r="R13" s="9" t="inlineStr">
@@ -1602,11 +1602,11 @@
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>1001812</v>
+        <v>1002236</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>REFRIGERANTE ANTICONG. X20 LT</t>
+          <t>BULON PARA CUCHILLA XUN</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>01-STOCK NULO</t>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
         </is>
       </c>
       <c r="J14" s="7" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="N14" s="8" t="n">
-        <v>210283.61</v>
+        <v>63148.11</v>
       </c>
       <c r="O14" s="5" t="inlineStr">
         <is>
@@ -1664,27 +1664,27 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>LUBRICANTES</t>
+          <t>DESGASTE</t>
         </is>
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>ADITIVOS</t>
+          <t>CAT 140K // CAT 988H // CAT D6T</t>
         </is>
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
-          <t>L02</t>
+          <t>G05</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="9" t="n">
-        <v>1001813</v>
+        <v>1002236</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>REFRIGERANTE CATERPILLAR X20L</t>
+          <t>BULON PARA CUCHILLA XUN</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -1703,29 +1703,29 @@
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr"/>
-      <c r="G15" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H15" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>V1</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>NO PLANIFICADO</t>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
         </is>
       </c>
       <c r="J15" s="11" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="L15" s="11" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="N15" s="12" t="n">
-        <v>539342.04</v>
+        <v>29912.26</v>
       </c>
       <c r="O15" s="10" t="inlineStr">
         <is>
@@ -1742,27 +1742,27 @@
       </c>
       <c r="P15" s="9" t="inlineStr">
         <is>
-          <t>LUBRICANTES</t>
+          <t>DESGASTE</t>
         </is>
       </c>
       <c r="Q15" s="9" t="inlineStr">
         <is>
-          <t>ADITIVOS</t>
+          <t>CAT 140K // CAT 988H // CAT D6T</t>
         </is>
       </c>
       <c r="R15" s="9" t="inlineStr">
         <is>
-          <t>L02</t>
+          <t>G05</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>1001895</v>
+        <v>1002340</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>ALCOHOL LIQUIDO X LITRO</t>
+          <t>BULON 5/8 X 21/2</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="J16" s="7" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>100</v>
+        <v>172</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="N16" s="8" t="n">
-        <v>40228.94</v>
+        <v>68294.47</v>
       </c>
       <c r="O16" s="5" t="inlineStr">
         <is>
@@ -1820,27 +1820,27 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>LIMPIEZA</t>
+          <t>DESGASTE</t>
         </is>
       </c>
       <c r="Q16" s="4" t="inlineStr">
         <is>
-          <t>ALCOHOL LIQUIDO</t>
+          <t>JD 770D/CAT 140K</t>
         </is>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>G05</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="9" t="n">
-        <v>1001895</v>
+        <v>1002353</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>ALCOHOL LIQUIDO X LITRO</t>
+          <t>TUERCA 5 8</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -1875,13 +1875,13 @@
         </is>
       </c>
       <c r="J17" s="11" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>100</v>
+        <v>172</v>
       </c>
       <c r="L17" s="11" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="N17" s="12" t="n">
-        <v>16762.06</v>
+        <v>147408.47</v>
       </c>
       <c r="O17" s="10" t="inlineStr">
         <is>
@@ -1898,27 +1898,27 @@
       </c>
       <c r="P17" s="9" t="inlineStr">
         <is>
-          <t>LIMPIEZA</t>
+          <t>DESGASTE</t>
         </is>
       </c>
       <c r="Q17" s="9" t="inlineStr">
         <is>
-          <t>ALCOHOL LIQUIDO</t>
+          <t>JD 770 670 CAT 140H</t>
         </is>
       </c>
       <c r="R17" s="9" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>G05</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>1002236</v>
+        <v>1003466</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>BULON PARA CUCHILLA XUN</t>
+          <t>PERTIGA 3.4M-3.7MC/LED/BANDSOP12/24v xUN</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -1953,13 +1953,13 @@
         </is>
       </c>
       <c r="J18" s="7" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="N18" s="8" t="n">
-        <v>39981.64</v>
+        <v>438919.32</v>
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
@@ -1976,27 +1976,27 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>DESGASTE</t>
+          <t>REPUESTOS</t>
         </is>
       </c>
       <c r="Q18" s="4" t="inlineStr">
         <is>
-          <t>CAT 140K // CAT 988H // CAT D6T</t>
+          <t>AUTOMOTOR</t>
         </is>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>G05</t>
+          <t>C03</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="9" t="n">
-        <v>1002236</v>
+        <v>1004256</v>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>BULON PARA CUCHILLA XUN</t>
+          <t>SEMIMASCARA X UN</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -2031,13 +2031,13 @@
         </is>
       </c>
       <c r="J19" s="11" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="L19" s="11" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="N19" s="12" t="n">
-        <v>18938.67</v>
+        <v>43167.8</v>
       </c>
       <c r="O19" s="10" t="inlineStr">
         <is>
@@ -2054,27 +2054,27 @@
       </c>
       <c r="P19" s="9" t="inlineStr">
         <is>
-          <t>DESGASTE</t>
+          <t>SEGURIDAD</t>
         </is>
       </c>
       <c r="Q19" s="9" t="inlineStr">
         <is>
-          <t>CAT 140K // CAT 988H // CAT D6T</t>
+          <t>ACCESORIO SEGURIDAD</t>
         </is>
       </c>
       <c r="R19" s="9" t="inlineStr">
         <is>
-          <t>G05</t>
+          <t>C28</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>1002340</v>
+        <v>1004590</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>BULON 5/8 X 21/2</t>
+          <t>SEGURO P T70286 3 4 P CUCHILLA</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -2109,13 +2109,13 @@
         </is>
       </c>
       <c r="J20" s="7" t="n">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>172</v>
+        <v>48</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         </is>
       </c>
       <c r="N20" s="8" t="n">
-        <v>68294.47</v>
+        <v>54240.28</v>
       </c>
       <c r="O20" s="5" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="Q20" s="4" t="inlineStr">
         <is>
-          <t>JD 770D/CAT 140K</t>
+          <t>JD850J</t>
         </is>
       </c>
       <c r="R20" s="4" t="inlineStr">
@@ -2148,11 +2148,11 @@
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="9" t="n">
-        <v>1002353</v>
+        <v>1009471</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>TUERCA 5 8</t>
+          <t>ANTEOJO TRANSPARENTE H/C</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -2187,13 +2187,13 @@
         </is>
       </c>
       <c r="J21" s="11" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>172</v>
+        <v>300</v>
       </c>
       <c r="L21" s="11" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="N21" s="12" t="n">
-        <v>147408.47</v>
+        <v>12917.94</v>
       </c>
       <c r="O21" s="10" t="inlineStr">
         <is>
@@ -2210,27 +2210,27 @@
       </c>
       <c r="P21" s="9" t="inlineStr">
         <is>
-          <t>DESGASTE</t>
+          <t>SEGURIDAD</t>
         </is>
       </c>
       <c r="Q21" s="9" t="inlineStr">
         <is>
-          <t>JD 770 670 CAT 140H</t>
+          <t>ACCESORIO SEGURIDAD</t>
         </is>
       </c>
       <c r="R21" s="9" t="inlineStr">
         <is>
-          <t>G05</t>
+          <t>C28</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>1004256</v>
+        <v>1009471</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>SEMIMASCARA X UN</t>
+          <t>ANTEOJO TRANSPARENTE H/C</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>01-STOCK NULO</t>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
         </is>
       </c>
       <c r="J22" s="7" t="n">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="N22" s="8" t="n">
-        <v>129503.39</v>
+        <v>40045.6</v>
       </c>
       <c r="O22" s="5" t="inlineStr">
         <is>
@@ -2304,11 +2304,11 @@
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="9" t="n">
-        <v>1004590</v>
+        <v>1009471</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>SEGURO P T70286 3 4 P CUCHILLA</t>
+          <t>ANTEOJO TRANSPARENTE H/C</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
@@ -2343,13 +2343,13 @@
         </is>
       </c>
       <c r="J23" s="11" t="n">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>48</v>
+        <v>300</v>
       </c>
       <c r="L23" s="11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>54240.28</v>
+        <v>24544.08</v>
       </c>
       <c r="O23" s="10" t="inlineStr">
         <is>
@@ -2366,27 +2366,27 @@
       </c>
       <c r="P23" s="9" t="inlineStr">
         <is>
-          <t>DESGASTE</t>
+          <t>SEGURIDAD</t>
         </is>
       </c>
       <c r="Q23" s="9" t="inlineStr">
         <is>
-          <t>JD850J</t>
+          <t>ACCESORIO SEGURIDAD</t>
         </is>
       </c>
       <c r="R23" s="9" t="inlineStr">
         <is>
-          <t>G05</t>
+          <t>C28</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>1009471</v>
+        <v>1009475</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>ANTEOJO TRANSPARENTE H/C</t>
+          <t>PANTALON TERMICO "ROJO" T M</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -2405,29 +2405,29 @@
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>V1</t>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>02-MENOR A PUNTO DE PEDIDO</t>
+          <t>NO PLANIFICADO</t>
         </is>
       </c>
       <c r="J24" s="7" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="N24" s="8" t="n">
-        <v>12917.94</v>
+        <v>57794.08</v>
       </c>
       <c r="O24" s="5" t="inlineStr">
         <is>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>SEGURIDAD</t>
+          <t>ROPA</t>
         </is>
       </c>
       <c r="Q24" s="4" t="inlineStr">
         <is>
-          <t>ACCESORIO SEGURIDAD</t>
+          <t>INDUMENTARIA -15</t>
         </is>
       </c>
       <c r="R24" s="4" t="inlineStr">
@@ -2460,11 +2460,11 @@
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="9" t="n">
-        <v>1009471</v>
+        <v>1009476</v>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>ANTEOJO TRANSPARENTE H/C</t>
+          <t>PANTALON TERMICO "ROJO" T L</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -2483,29 +2483,29 @@
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>V1</t>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>02-MENOR A PUNTO DE PEDIDO</t>
+          <t>NO PLANIFICADO</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="L25" s="11" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>40045.6</v>
+        <v>206590.8</v>
       </c>
       <c r="O25" s="10" t="inlineStr">
         <is>
@@ -2522,12 +2522,12 @@
       </c>
       <c r="P25" s="9" t="inlineStr">
         <is>
-          <t>SEGURIDAD</t>
+          <t>ROPA</t>
         </is>
       </c>
       <c r="Q25" s="9" t="inlineStr">
         <is>
-          <t>ACCESORIO SEGURIDAD</t>
+          <t>INDUMENTARIA -15</t>
         </is>
       </c>
       <c r="R25" s="9" t="inlineStr">
@@ -2538,11 +2538,11 @@
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>1009471</v>
+        <v>1009478</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>ANTEOJO TRANSPARENTE H/C</t>
+          <t>PANTALON TERMICO "ROJO" T XXL</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -2561,29 +2561,29 @@
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>V1</t>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>02-MENOR A PUNTO DE PEDIDO</t>
+          <t>NO PLANIFICADO</t>
         </is>
       </c>
       <c r="J26" s="7" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="L26" s="7" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N26" s="8" t="n">
-        <v>24544.08</v>
+        <v>96814.36</v>
       </c>
       <c r="O26" s="5" t="inlineStr">
         <is>
@@ -2600,12 +2600,12 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>SEGURIDAD</t>
+          <t>ROPA</t>
         </is>
       </c>
       <c r="Q26" s="4" t="inlineStr">
         <is>
-          <t>ACCESORIO SEGURIDAD</t>
+          <t>INDUMENTARIA -15</t>
         </is>
       </c>
       <c r="R26" s="4" t="inlineStr">
@@ -2616,11 +2616,11 @@
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="9" t="n">
-        <v>1009475</v>
+        <v>1009479</v>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>PANTALON TERMICO "ROJO" T M</t>
+          <t>PANTALON TERMICO "ROJO" T XXXL</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -2661,7 +2661,7 @@
         <v>0</v>
       </c>
       <c r="L27" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>57794.08</v>
+        <v>90737.21000000001</v>
       </c>
       <c r="O27" s="10" t="inlineStr">
         <is>
@@ -2694,11 +2694,11 @@
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="4" t="n">
-        <v>1009476</v>
+        <v>1009479</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>PANTALON TERMICO "ROJO" T L</t>
+          <t>PANTALON TERMICO "ROJO" T XXXL</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -2739,7 +2739,7 @@
         <v>0</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="N28" s="8" t="n">
-        <v>206590.8</v>
+        <v>30245.74</v>
       </c>
       <c r="O28" s="5" t="inlineStr">
         <is>
@@ -2772,11 +2772,11 @@
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="9" t="n">
-        <v>1009478</v>
+        <v>1009481</v>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>PANTALON TERMICO "ROJO" T XXL</t>
+          <t>ANTEOJO GRIS H/C</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -2795,29 +2795,29 @@
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr"/>
-      <c r="G29" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H29" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>V1</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>NO PLANIFICADO</t>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L29" s="11" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>96814.36</v>
+        <v>26502.63</v>
       </c>
       <c r="O29" s="10" t="inlineStr">
         <is>
@@ -2834,12 +2834,12 @@
       </c>
       <c r="P29" s="9" t="inlineStr">
         <is>
-          <t>ROPA</t>
+          <t>SEGURIDAD</t>
         </is>
       </c>
       <c r="Q29" s="9" t="inlineStr">
         <is>
-          <t>INDUMENTARIA -15</t>
+          <t>INDUMENTARIA</t>
         </is>
       </c>
       <c r="R29" s="9" t="inlineStr">
@@ -2850,11 +2850,11 @@
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="4" t="n">
-        <v>1009479</v>
+        <v>1009481</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>PANTALON TERMICO "ROJO" T XXXL</t>
+          <t>ANTEOJO GRIS H/C</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -2873,29 +2873,29 @@
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H30" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>V1</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>NO PLANIFICADO</t>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
         </is>
       </c>
       <c r="J30" s="7" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="N30" s="8" t="n">
-        <v>90737.21000000001</v>
+        <v>64931.44</v>
       </c>
       <c r="O30" s="5" t="inlineStr">
         <is>
@@ -2912,12 +2912,12 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>ROPA</t>
+          <t>SEGURIDAD</t>
         </is>
       </c>
       <c r="Q30" s="4" t="inlineStr">
         <is>
-          <t>INDUMENTARIA -15</t>
+          <t>INDUMENTARIA</t>
         </is>
       </c>
       <c r="R30" s="4" t="inlineStr">
@@ -2928,11 +2928,11 @@
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="9" t="n">
-        <v>1009479</v>
+        <v>1009530</v>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>PANTALON TERMICO "ROJO" T XXXL</t>
+          <t>BATERIAS DE REPUESTO P/BALIZA 1000 HORAS</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -2951,29 +2951,29 @@
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr"/>
-      <c r="G31" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H31" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>V1</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>NO PLANIFICADO</t>
+          <t>04-MAYOR A STOCK MAXIMO</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L31" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M31" s="10" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>30245.74</v>
+        <v>12294.06</v>
       </c>
       <c r="O31" s="10" t="inlineStr">
         <is>
@@ -2990,27 +2990,27 @@
       </c>
       <c r="P31" s="9" t="inlineStr">
         <is>
-          <t>ROPA</t>
+          <t>SEGURIDAD</t>
         </is>
       </c>
       <c r="Q31" s="9" t="inlineStr">
         <is>
-          <t>INDUMENTARIA -15</t>
+          <t>INSUMOS</t>
         </is>
       </c>
       <c r="R31" s="9" t="inlineStr">
         <is>
-          <t>C28</t>
+          <t>C03</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="4" t="n">
-        <v>1009481</v>
+        <v>1009530</v>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>ANTEOJO GRIS H/C</t>
+          <t>BATERIAS DE REPUESTO P/BALIZA 1000 HORAS</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>02-MENOR A PUNTO DE PEDIDO</t>
+          <t>04-MAYOR A STOCK MAXIMO</t>
         </is>
       </c>
       <c r="J32" s="7" t="n">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="N32" s="8" t="n">
-        <v>26502.63</v>
+        <v>159822.76</v>
       </c>
       <c r="O32" s="5" t="inlineStr">
         <is>
@@ -3073,27 +3073,27 @@
       </c>
       <c r="Q32" s="4" t="inlineStr">
         <is>
-          <t>INDUMENTARIA</t>
+          <t>INSUMOS</t>
         </is>
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>C28</t>
+          <t>C03</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="9" t="n">
-        <v>1009481</v>
+        <v>1012896</v>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>ANTEOJO GRIS H/C</t>
+          <t>INSUMO FERRETERIA S DETALLE</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>ZSTO</t>
+          <t>ZGEN</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
@@ -3107,29 +3107,29 @@
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>V1</t>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>02-MENOR A PUNTO DE PEDIDO</t>
+          <t>NO PLANIFICADO</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="L33" s="11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M33" s="10" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>64931.43</v>
+        <v>0</v>
       </c>
       <c r="O33" s="10" t="inlineStr">
         <is>
@@ -3146,32 +3146,28 @@
       </c>
       <c r="P33" s="9" t="inlineStr">
         <is>
-          <t>SEGURIDAD</t>
-        </is>
-      </c>
-      <c r="Q33" s="9" t="inlineStr">
-        <is>
-          <t>INDUMENTARIA</t>
-        </is>
-      </c>
+          <t>SIN RUBRO</t>
+        </is>
+      </c>
+      <c r="Q33" s="9" t="inlineStr"/>
       <c r="R33" s="9" t="inlineStr">
         <is>
-          <t>C28</t>
+          <t>C13</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="4" t="n">
-        <v>1009530</v>
+        <v>1012896</v>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>BATERIAS DE REPUESTO P/BALIZA 1000 HORAS</t>
+          <t>INSUMO FERRETERIA S DETALLE</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>ZSTO</t>
+          <t>ZGEN</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -3185,29 +3181,29 @@
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr"/>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>V1</t>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>04-MAYOR A STOCK MAXIMO</t>
+          <t>NO PLANIFICADO</t>
         </is>
       </c>
       <c r="J34" s="7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
@@ -3215,7 +3211,7 @@
         </is>
       </c>
       <c r="N34" s="8" t="n">
-        <v>12294.06</v>
+        <v>0</v>
       </c>
       <c r="O34" s="5" t="inlineStr">
         <is>
@@ -3224,32 +3220,28 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>SEGURIDAD</t>
-        </is>
-      </c>
-      <c r="Q34" s="4" t="inlineStr">
-        <is>
-          <t>INSUMOS</t>
-        </is>
-      </c>
+          <t>SIN RUBRO</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="inlineStr"/>
       <c r="R34" s="4" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>C13</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="9" t="n">
-        <v>1009530</v>
+        <v>1015947</v>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>BATERIAS DE REPUESTO P/BALIZA 1000 HORAS</t>
+          <t>REPUESTO GENERICO</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>ZSTO</t>
+          <t>ZGEN</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
@@ -3263,29 +3255,29 @@
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr"/>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>V1</t>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>04-MAYOR A STOCK MAXIMO</t>
+          <t>NO PLANIFICADO</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L35" s="11" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="M35" s="10" t="inlineStr">
         <is>
@@ -3293,7 +3285,7 @@
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>159822.76</v>
+        <v>0</v>
       </c>
       <c r="O35" s="10" t="inlineStr">
         <is>
@@ -3302,14 +3294,10 @@
       </c>
       <c r="P35" s="9" t="inlineStr">
         <is>
-          <t>SEGURIDAD</t>
-        </is>
-      </c>
-      <c r="Q35" s="9" t="inlineStr">
-        <is>
-          <t>INSUMOS</t>
-        </is>
-      </c>
+          <t>SIN RUBRO</t>
+        </is>
+      </c>
+      <c r="Q35" s="9" t="inlineStr"/>
       <c r="R35" s="9" t="inlineStr">
         <is>
           <t>C03</t>
@@ -3318,11 +3306,11 @@
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="4" t="n">
-        <v>1012896</v>
+        <v>1015947</v>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>INSUMO FERRETERIA S DETALLE</t>
+          <t>REPUESTO GENERICO</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -3363,7 +3351,7 @@
         <v>0</v>
       </c>
       <c r="L36" s="7" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
@@ -3386,22 +3374,22 @@
       <c r="Q36" s="4" t="inlineStr"/>
       <c r="R36" s="4" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>C03</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="9" t="n">
-        <v>1012896</v>
+        <v>1016479</v>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>INSUMO FERRETERIA S DETALLE</t>
+          <t>PROTECTOR SOLAR CREMA 60FPS X120ML</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>ZGEN</t>
+          <t>ZSCD</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
@@ -3415,29 +3403,29 @@
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr"/>
-      <c r="G37" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H37" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>V1</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>NO PLANIFICADO</t>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L37" s="11" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="M37" s="10" t="inlineStr">
         <is>
@@ -3445,7 +3433,7 @@
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>0</v>
+        <v>322332.88</v>
       </c>
       <c r="O37" s="10" t="inlineStr">
         <is>
@@ -3454,28 +3442,32 @@
       </c>
       <c r="P37" s="9" t="inlineStr">
         <is>
-          <t>SIN RUBRO</t>
-        </is>
-      </c>
-      <c r="Q37" s="9" t="inlineStr"/>
+          <t>SEGURIDAD</t>
+        </is>
+      </c>
+      <c r="Q37" s="9" t="inlineStr">
+        <is>
+          <t>INSUMO</t>
+        </is>
+      </c>
       <c r="R37" s="9" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>C28</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="4" t="n">
-        <v>1015947</v>
+        <v>1016480</v>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>REPUESTO GENERICO</t>
+          <t>PROTECTOR SOLAR LABIAL 50FPS X4,8G</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>ZGEN</t>
+          <t>ZSCD</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -3489,29 +3481,29 @@
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr"/>
-      <c r="G38" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H38" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>V1</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>NO PLANIFICADO</t>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
         </is>
       </c>
       <c r="J38" s="7" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L38" s="7" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
@@ -3519,7 +3511,7 @@
         </is>
       </c>
       <c r="N38" s="8" t="n">
-        <v>0</v>
+        <v>138945.97</v>
       </c>
       <c r="O38" s="5" t="inlineStr">
         <is>
@@ -3528,13 +3520,17 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>SIN RUBRO</t>
-        </is>
-      </c>
-      <c r="Q38" s="4" t="inlineStr"/>
+          <t>SEGURIDAD</t>
+        </is>
+      </c>
+      <c r="Q38" s="4" t="inlineStr">
+        <is>
+          <t>INSUMO</t>
+        </is>
+      </c>
       <c r="R38" s="4" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>C28</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3955,7 @@
         <v>500</v>
       </c>
       <c r="L44" s="7" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
@@ -3967,7 +3963,7 @@
         </is>
       </c>
       <c r="N44" s="8" t="n">
-        <v>229469.75</v>
+        <v>16997.76</v>
       </c>
       <c r="O44" s="5" t="inlineStr">
         <is>
@@ -4027,7 +4023,7 @@
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
-          <t>01-STOCK NULO</t>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
@@ -4115,7 +4111,7 @@
         <v>350</v>
       </c>
       <c r="L46" s="7" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
@@ -4123,7 +4119,7 @@
         </is>
       </c>
       <c r="N46" s="8" t="n">
-        <v>125226.19</v>
+        <v>104343.85</v>
       </c>
       <c r="O46" s="5" t="inlineStr">
         <is>
@@ -4201,7 +4197,7 @@
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>104355.16</v>
+        <v>104343.85</v>
       </c>
       <c r="O47" s="10" t="inlineStr">
         <is>
@@ -4573,7 +4569,7 @@
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>01-STOCK NULO</t>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
         </is>
       </c>
       <c r="J52" s="7" t="n">
@@ -4690,11 +4686,11 @@
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="4" t="n">
-        <v>1041725</v>
+        <v>1056086</v>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>CUCHILLA (7′ X 8″ X 5/8″) X 15 Aguj 5/8"</t>
+          <t>BOLIGRAFO TRAZO GRUESO AZUL</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -4725,17 +4721,17 @@
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>02-MENOR A PUNTO DE PEDIDO</t>
+          <t>03-MAYOR A PUNTO DE PEDIDO</t>
         </is>
       </c>
       <c r="J54" s="7" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K54" s="7" t="n">
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="L54" s="7" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
@@ -4743,7 +4739,7 @@
         </is>
       </c>
       <c r="N54" s="8" t="n">
-        <v>376920.88</v>
+        <v>13456.28</v>
       </c>
       <c r="O54" s="5" t="inlineStr">
         <is>
@@ -4752,17 +4748,17 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>EQUIPOS</t>
+          <t>LIBRERIA</t>
         </is>
       </c>
       <c r="Q54" s="4" t="inlineStr">
         <is>
-          <t>DESGASTE</t>
+          <t>ESCRITURA</t>
         </is>
       </c>
       <c r="R54" s="4" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>C17</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4809,7 @@
         <v>400</v>
       </c>
       <c r="L55" s="11" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="M55" s="10" t="inlineStr">
         <is>
@@ -4821,7 +4817,7 @@
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>16044.03</v>
+        <v>10350.99</v>
       </c>
       <c r="O55" s="10" t="inlineStr">
         <is>
@@ -4846,11 +4842,11 @@
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="4" t="n">
-        <v>1056086</v>
+        <v>1056088</v>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>BOLIGRAFO TRAZO GRUESO AZUL</t>
+          <t>BOLIGRAFO TRAZO GRUESO NEGRO</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -4881,17 +4877,17 @@
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>03-MAYOR A PUNTO DE PEDIDO</t>
+          <t>02-MENOR A PUNTO DE PEDIDO</t>
         </is>
       </c>
       <c r="J56" s="7" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="L56" s="7" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
@@ -4899,7 +4895,7 @@
         </is>
       </c>
       <c r="N56" s="8" t="n">
-        <v>10350.99</v>
+        <v>2439.75</v>
       </c>
       <c r="O56" s="5" t="inlineStr">
         <is>
@@ -4922,358 +4918,8 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="9" t="n">
-        <v>1056088</v>
-      </c>
-      <c r="B57" s="9" t="inlineStr">
-        <is>
-          <t>BOLIGRAFO TRAZO GRUESO NEGRO</t>
-        </is>
-      </c>
-      <c r="C57" s="10" t="inlineStr">
-        <is>
-          <t>ZSTO</t>
-        </is>
-      </c>
-      <c r="D57" s="10" t="inlineStr">
-        <is>
-          <t>MM01</t>
-        </is>
-      </c>
-      <c r="E57" s="10" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="F57" s="10" t="inlineStr"/>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>V1</t>
-        </is>
-      </c>
-      <c r="I57" s="9" t="inlineStr">
-        <is>
-          <t>01-STOCK NULO</t>
-        </is>
-      </c>
-      <c r="J57" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="K57" s="11" t="n">
-        <v>200</v>
-      </c>
-      <c r="L57" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="M57" s="10" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="N57" s="12" t="n">
-        <v>2439.75</v>
-      </c>
-      <c r="O57" s="10" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="P57" s="9" t="inlineStr">
-        <is>
-          <t>LIBRERIA</t>
-        </is>
-      </c>
-      <c r="Q57" s="9" t="inlineStr">
-        <is>
-          <t>ESCRITURA</t>
-        </is>
-      </c>
-      <c r="R57" s="9" t="inlineStr">
-        <is>
-          <t>C17</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>M00501</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>SIN DESCRIPCIÓN</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr"/>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>MM01</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="inlineStr"/>
-      <c r="G58" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H58" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I58" s="4" t="inlineStr">
-        <is>
-          <t>NO PLANIFICADO</t>
-        </is>
-      </c>
-      <c r="J58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M58" s="5" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="N58" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="5" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="P58" s="4" t="inlineStr">
-        <is>
-          <t>SIN RUBRO</t>
-        </is>
-      </c>
-      <c r="Q58" s="4" t="inlineStr"/>
-      <c r="R58" s="4" t="inlineStr"/>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="9" t="inlineStr">
-        <is>
-          <t>M00601</t>
-        </is>
-      </c>
-      <c r="B59" s="9" t="inlineStr">
-        <is>
-          <t>SIN DESCRIPCIÓN</t>
-        </is>
-      </c>
-      <c r="C59" s="10" t="inlineStr"/>
-      <c r="D59" s="10" t="inlineStr">
-        <is>
-          <t>MM01</t>
-        </is>
-      </c>
-      <c r="E59" s="10" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="F59" s="10" t="inlineStr"/>
-      <c r="G59" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H59" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>NO PLANIFICADO</t>
-        </is>
-      </c>
-      <c r="J59" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M59" s="10" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="N59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="10" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="P59" s="9" t="inlineStr">
-        <is>
-          <t>SIN RUBRO</t>
-        </is>
-      </c>
-      <c r="Q59" s="9" t="inlineStr"/>
-      <c r="R59" s="9" t="inlineStr"/>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>M00701</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>SIN DESCRIPCIÓN</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr"/>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>MM01</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="inlineStr"/>
-      <c r="G60" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H60" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I60" s="4" t="inlineStr">
-        <is>
-          <t>NO PLANIFICADO</t>
-        </is>
-      </c>
-      <c r="J60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M60" s="5" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="N60" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="5" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="P60" s="4" t="inlineStr">
-        <is>
-          <t>SIN RUBRO</t>
-        </is>
-      </c>
-      <c r="Q60" s="4" t="inlineStr"/>
-      <c r="R60" s="4" t="inlineStr"/>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="9" t="inlineStr">
-        <is>
-          <t>M00901</t>
-        </is>
-      </c>
-      <c r="B61" s="9" t="inlineStr">
-        <is>
-          <t>SIN DESCRIPCIÓN</t>
-        </is>
-      </c>
-      <c r="C61" s="10" t="inlineStr"/>
-      <c r="D61" s="10" t="inlineStr">
-        <is>
-          <t>MM01</t>
-        </is>
-      </c>
-      <c r="E61" s="10" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="F61" s="10" t="inlineStr"/>
-      <c r="G61" s="13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H61" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>NO PLANIFICADO</t>
-        </is>
-      </c>
-      <c r="J61" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M61" s="10" t="inlineStr">
-        <is>
-          <t>UN</t>
-        </is>
-      </c>
-      <c r="N61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="10" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="P61" s="9" t="inlineStr">
-        <is>
-          <t>SIN RUBRO</t>
-        </is>
-      </c>
-      <c r="Q61" s="9" t="inlineStr"/>
-      <c r="R61" s="9" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:R61"/>
+  <autoFilter ref="A1:R56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>